--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1099,13 +1099,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE9A7751-EF70-4BA0-AAA3-3E81C079D78F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA93FF25-030C-4C55-824B-1922886D982B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEF3D36-8318-43D3-8132-FFB52BD50D50}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD10B2D4-06E9-43FD-BE1D-C42F694D3121}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2452C730-D35C-4E83-829B-433EEF74297D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9F6BF8E-D757-486E-9E91-9445EA2454FF}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1099,13 +1099,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA93FF25-030C-4C55-824B-1922886D982B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B65689A6-EAAD-47FB-BDF9-BAD0EE248208}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD10B2D4-06E9-43FD-BE1D-C42F694D3121}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2196EC6-65B0-4FF8-87CF-E9EA90D36282}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9F6BF8E-D757-486E-9E91-9445EA2454FF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB0EC11E-53D7-4B56-9CD9-EBB9BDD65CBB}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1099,13 +1099,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B65689A6-EAAD-47FB-BDF9-BAD0EE248208}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48D0C8AD-32A9-4C24-B67F-DB4AAD81C9DC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2196EC6-65B0-4FF8-87CF-E9EA90D36282}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{805C773F-68C0-4013-ABD0-C6643E5A65C3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB0EC11E-53D7-4B56-9CD9-EBB9BDD65CBB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E42108D9-1BFC-49CA-8207-12FF27EBC51E}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1099,13 +1099,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48D0C8AD-32A9-4C24-B67F-DB4AAD81C9DC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B532C46-9777-4DE6-BC45-52F0671B16AD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{805C773F-68C0-4013-ABD0-C6643E5A65C3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{029A9679-0E01-43BC-98B4-B9AD0E7F2FF0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E42108D9-1BFC-49CA-8207-12FF27EBC51E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF2BD375-D1BF-429A-BB13-5A52E7E73C13}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -11,6 +11,86 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="25">
+  <si>
+    <t>species_sci</t>
+  </si>
+  <si>
+    <t>Species</t>
+  </si>
+  <si>
+    <t>V1_neuron_density_per_mm2</t>
+  </si>
+  <si>
+    <t>V1_mitochondria_density_per_mm2</t>
+  </si>
+  <si>
+    <t>V1_synapse_density_per_mm2</t>
+  </si>
+  <si>
+    <t>V1_PSD_length_nm</t>
+  </si>
+  <si>
+    <t>Bettongia penicillata</t>
+  </si>
+  <si>
+    <t>Choloepus didactylus</t>
+  </si>
+  <si>
+    <t>Dinomys branickii</t>
+  </si>
+  <si>
+    <t>Giraffa camelopardalis</t>
+  </si>
+  <si>
+    <t>Homo sapiens</t>
+  </si>
+  <si>
+    <t>Lemur catta</t>
+  </si>
+  <si>
+    <t>Loxodonta africana</t>
+  </si>
+  <si>
+    <t>Notamacropus rufogriseus</t>
+  </si>
+  <si>
+    <t>Macropus rufogriseus</t>
+  </si>
+  <si>
+    <t>Mus musculus</t>
+  </si>
+  <si>
+    <t>Myrmecophaga tridactyla</t>
+  </si>
+  <si>
+    <t>Neofelis nebulosa</t>
+  </si>
+  <si>
+    <t>Pan troglodytes</t>
+  </si>
+  <si>
+    <t>Papio anubis</t>
+  </si>
+  <si>
+    <t>Procavia capensis</t>
+  </si>
+  <si>
+    <t>Rangifer tarandus</t>
+  </si>
+  <si>
+    <t>Saimiri sciureus</t>
+  </si>
+  <si>
+    <t>Trichechus manatus</t>
+  </si>
+  <si>
+    <t>Ursus arctos</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -354,48 +434,32 @@
   <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>species_sci</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Species</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>V1_neuron_density_per_mm2</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>V1_mitochondria_density_per_mm2</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>V1_synapse_density_per_mm2</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>V1_PSD_length_nm</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Bettongia penicillata</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Bettongia penicillata</t>
-        </is>
+    <row r="1" spans="1:6" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
       </c>
       <c r="C2">
         <v>40447</v>
@@ -410,16 +474,12 @@
         <v>388</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Choloepus didactylus</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Choloepus didactylus</t>
-        </is>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
       </c>
       <c r="C3">
         <v>17425</v>
@@ -434,16 +494,12 @@
         <v>350</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Dinomys branickii</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Dinomys branickii</t>
-        </is>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
       </c>
       <c r="C4">
         <v>13537</v>
@@ -458,16 +514,12 @@
         <v>359</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Giraffa camelopardalis</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Giraffa camelopardalis</t>
-        </is>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
       </c>
       <c r="C5">
         <v>10350</v>
@@ -482,16 +534,12 @@
         <v>344</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Homo sapiens</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Homo sapiens</t>
-        </is>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
       </c>
       <c r="C6">
         <v>7258</v>
@@ -506,16 +554,12 @@
         <v>352</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Lemur catta</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Lemur catta</t>
-        </is>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
       </c>
       <c r="C7">
         <v>29398</v>
@@ -530,16 +574,12 @@
         <v>317</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Loxodonta africana</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Loxodonta africana</t>
-        </is>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
       </c>
       <c r="C8">
         <v>3119</v>
@@ -554,16 +594,12 @@
         <v>310</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Notamacropus rufogriseus</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Macropus rufogriseus</t>
-        </is>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
       </c>
       <c r="C9">
         <v>23211</v>
@@ -578,16 +614,12 @@
         <v>322</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Mus musculus</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Mus musculus</t>
-        </is>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
       </c>
       <c r="C10">
         <v>53681</v>
@@ -602,16 +634,12 @@
         <v>262</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Myrmecophaga tridactyla</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Myrmecophaga tridactyla</t>
-        </is>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
       </c>
       <c r="C11">
         <v>11234</v>
@@ -626,16 +654,12 @@
         <v>378</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Neofelis nebulosa</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Neofelis nebulosa</t>
-        </is>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
       </c>
       <c r="C12">
         <v>13736</v>
@@ -650,16 +674,12 @@
         <v>332</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Pan troglodytes</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Pan troglodytes</t>
-        </is>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
       </c>
       <c r="C13">
         <v>11030</v>
@@ -674,16 +694,12 @@
         <v>339</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Papio anubis</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Papio anubis</t>
-        </is>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
       </c>
       <c r="C14">
         <v>10495</v>
@@ -698,16 +714,12 @@
         <v>299</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Procavia capensis</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Procavia capensis</t>
-        </is>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
       </c>
       <c r="C15">
         <v>28971</v>
@@ -722,16 +734,12 @@
         <v>331</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Rangifer tarandus</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Rangifer tarandus</t>
-        </is>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
       </c>
       <c r="C16">
         <v>6635</v>
@@ -746,16 +754,12 @@
         <v>333</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Saimiri sciureus</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Saimiri sciureus</t>
-        </is>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
       </c>
       <c r="C17">
         <v>14911</v>
@@ -770,16 +774,12 @@
         <v>307</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Trichechus manatus</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Trichechus manatus</t>
-        </is>
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
       </c>
       <c r="C18">
         <v>6258</v>
@@ -794,16 +794,12 @@
         <v>361</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Ursus arctos</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Ursus arctos</t>
-        </is>
+    <row r="19" spans="1:6">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
       </c>
       <c r="C19">
         <v>9268</v>
@@ -1099,13 +1095,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B532C46-9777-4DE6-BC45-52F0671B16AD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{644E8E9D-6CA0-4CDF-B3F9-9D9CB17EB473}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{029A9679-0E01-43BC-98B4-B9AD0E7F2FF0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4DF7F53-43F2-4068-9E62-798034481DD3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF2BD375-D1BF-429A-BB13-5A52E7E73C13}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6213FB34-E028-465E-94E8-1534D8CA78DC}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1095,13 +1095,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{644E8E9D-6CA0-4CDF-B3F9-9D9CB17EB473}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61D5BC9B-1005-45EE-B0D5-EBD34C588351}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4DF7F53-43F2-4068-9E62-798034481DD3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7E163DF-E749-4814-ACD2-FDEF902F335A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6213FB34-E028-465E-94E8-1534D8CA78DC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{920A586A-5B00-4F93-A480-61669F473F9F}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1095,13 +1095,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61D5BC9B-1005-45EE-B0D5-EBD34C588351}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5A94CBF-3C6B-41CE-BF70-39B2B3037D2A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7E163DF-E749-4814-ACD2-FDEF902F335A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{091E9265-1F4E-4BC0-A5BC-4C0DA2DF32FF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{920A586A-5B00-4F93-A480-61669F473F9F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08726E05-097A-4781-92A7-F681C6147B38}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -817,291 +817,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5A94CBF-3C6B-41CE-BF70-39B2B3037D2A}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{091E9265-1F4E-4BC0-A5BC-4C0DA2DF32FF}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08726E05-097A-4781-92A7-F681C6147B38}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -817,4 +817,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AC53522-30C9-4818-BFA3-19192FBB1CBC}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F44BD806-1F53-4347-9F5E-16A63DC6D96C}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F37FE64-BB12-427E-A657-1A0CB9F11327}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -817,291 +817,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AC53522-30C9-4818-BFA3-19192FBB1CBC}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F44BD806-1F53-4347-9F5E-16A63DC6D96C}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F37FE64-BB12-427E-A657-1A0CB9F11327}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -817,4 +817,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA5A3C2D-A2CC-4BAB-887B-2B198DA1E9DC}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EE41B5E-2752-4E39-9AC4-19E4CEB97F8D}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5B47D91-8709-4222-8A3A-72BA3A7E8022}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1095,13 +1095,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA5A3C2D-A2CC-4BAB-887B-2B198DA1E9DC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B628AF-F69A-44F1-8727-07894909732D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EE41B5E-2752-4E39-9AC4-19E4CEB97F8D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01B3A751-7631-4587-9876-738BF53D706D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5B47D91-8709-4222-8A3A-72BA3A7E8022}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0BBB216-5971-4805-83B2-713F7F538E96}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1095,13 +1095,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B628AF-F69A-44F1-8727-07894909732D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E249A20-5997-475E-86CC-AFCB8260B54C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01B3A751-7631-4587-9876-738BF53D706D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7857CA2-5100-48BC-8E29-0BA01028B165}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0BBB216-5971-4805-83B2-713F7F538E96}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC76F86F-D6E9-43F4-8066-558DD3C24B65}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1095,13 +1095,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E249A20-5997-475E-86CC-AFCB8260B54C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12748EDB-391A-487E-B769-6CB1C0EE6E9B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7857CA2-5100-48BC-8E29-0BA01028B165}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A338DE97-8CB9-4CC1-95A3-467F19A85E96}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC76F86F-D6E9-43F4-8066-558DD3C24B65}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4B627A8-059D-4918-BC81-31869B7FF021}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1095,13 +1095,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12748EDB-391A-487E-B769-6CB1C0EE6E9B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0733FD4B-70DE-41DF-8CBA-E8E065B9790E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A338DE97-8CB9-4CC1-95A3-467F19A85E96}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D49A0B45-50F4-47C1-BD9D-F636EC839234}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4B627A8-059D-4918-BC81-31869B7FF021}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBFEADDD-1A03-4652-BB94-54F124113AF2}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1095,13 +1095,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0733FD4B-70DE-41DF-8CBA-E8E065B9790E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33368C52-7751-4235-8FFE-8618E5F7BE1E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D49A0B45-50F4-47C1-BD9D-F636EC839234}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36ABBCF0-48AC-49D5-A0BA-307955745A81}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBFEADDD-1A03-4652-BB94-54F124113AF2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{304F3F32-EA2D-45D4-BE89-AA9E844727D0}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -817,291 +817,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33368C52-7751-4235-8FFE-8618E5F7BE1E}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36ABBCF0-48AC-49D5-A0BA-307955745A81}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{304F3F32-EA2D-45D4-BE89-AA9E844727D0}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -817,4 +817,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{494E6003-5A07-4F26-AFE0-60A13E2D6437}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7973D63-47C0-44B0-B95C-7D7E7EBB646B}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48CCC656-1E90-4083-AC63-5BD9315C9DCB}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1095,13 +1095,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{494E6003-5A07-4F26-AFE0-60A13E2D6437}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7072E8B1-F641-4A57-B5A2-C05D644CFEB9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7973D63-47C0-44B0-B95C-7D7E7EBB646B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DBFDB6B-3779-4653-B751-D0D2242A85C7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48CCC656-1E90-4083-AC63-5BD9315C9DCB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3ACA9520-CEF1-4AF1-9991-B5466B7D890D}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1095,13 +1095,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7072E8B1-F641-4A57-B5A2-C05D644CFEB9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E32EEB7-E4AC-46D6-8A84-0F9F0D2DB7F6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DBFDB6B-3779-4653-B751-D0D2242A85C7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC2C5EDA-D350-4BB5-ABE4-6936937402C7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3ACA9520-CEF1-4AF1-9991-B5466B7D890D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7F8E198-8CCC-44DC-94FD-105963F44149}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1095,13 +1095,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E32EEB7-E4AC-46D6-8A84-0F9F0D2DB7F6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFFA7216-62B9-4DF2-A5A6-B50EBD275BA0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC2C5EDA-D350-4BB5-ABE4-6936937402C7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{170C1E11-D0A9-40BF-87B9-9E23CE26C174}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7F8E198-8CCC-44DC-94FD-105963F44149}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3571975-6581-40E3-A052-EF3B20235E16}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1095,13 +1095,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFFA7216-62B9-4DF2-A5A6-B50EBD275BA0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D328B3E-635D-4D83-9161-565F8A631784}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{170C1E11-D0A9-40BF-87B9-9E23CE26C174}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{128542AB-C82A-4074-89A2-B02C479B6DDC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3571975-6581-40E3-A052-EF3B20235E16}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{066473A5-20CB-4921-BFB6-F13BB27EE7FC}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1095,13 +1095,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D328B3E-635D-4D83-9161-565F8A631784}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781B5A71-4C4D-47D1-80BD-49195E1FFD22}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{128542AB-C82A-4074-89A2-B02C479B6DDC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{123C026C-C663-44FF-8E54-0A8C5EC52CA9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{066473A5-20CB-4921-BFB6-F13BB27EE7FC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6FCCD2D-4D59-4760-92C7-7BA1DCEFA590}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -817,291 +817,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781B5A71-4C4D-47D1-80BD-49195E1FFD22}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{123C026C-C663-44FF-8E54-0A8C5EC52CA9}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6FCCD2D-4D59-4760-92C7-7BA1DCEFA590}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -817,4 +817,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2B30F1A-0A54-4EDF-9FDC-A04636B4142B}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D2100CB-8016-4F51-88D8-23932A952C01}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DEF30B8F-A452-4FC9-9F46-1E22CB2BEC2C}"/>
 </file>